--- a/team_mapping.xlsx
+++ b/team_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maslo\goalmind-pro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF7B438-243A-4B27-AB84-8944F4529417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF68731-2665-4C25-8D96-1152F0D106E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="492">
   <si>
     <t>fd_name</t>
   </si>
@@ -1484,6 +1484,18 @@
   </si>
   <si>
     <t>PEC Zwolle</t>
+  </si>
+  <si>
+    <t>Accrington ST</t>
+  </si>
+  <si>
+    <t>Boston United</t>
+  </si>
+  <si>
+    <t>Exeter City</t>
+  </si>
+  <si>
+    <t>Ayr Utd</t>
   </si>
 </sst>
 </file>
@@ -1898,6 +1910,9 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
+      <c r="B7" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -2127,6 +2142,9 @@
       <c r="A39" t="s">
         <v>39</v>
       </c>
+      <c r="B39" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -2273,6 +2291,9 @@
       <c r="A58" t="s">
         <v>58</v>
       </c>
+      <c r="B58" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -2860,6 +2881,9 @@
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">

--- a/team_mapping.xlsx
+++ b/team_mapping.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maslo\goalmind-pro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF68731-2665-4C25-8D96-1152F0D106E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB603DF5-AD83-429E-B50F-8F12EDFE4A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="504">
   <si>
     <t>fd_name</t>
   </si>
@@ -1496,6 +1496,54 @@
   </si>
   <si>
     <t>Ayr Utd</t>
+  </si>
+  <si>
+    <t>Airdrie United</t>
+  </si>
+  <si>
+    <t>Alloa Athletic</t>
+  </si>
+  <si>
+    <t>Elgin City</t>
+  </si>
+  <si>
+    <t>Forfar Athletic</t>
+  </si>
+  <si>
+    <t>Inverness CT</t>
+  </si>
+  <si>
+    <t>Queen of the South</t>
+  </si>
+  <si>
+    <t>Queen's Park</t>
+  </si>
+  <si>
+    <t>Stockport County</t>
+  </si>
+  <si>
+    <t>Yeovil Town</t>
+  </si>
+  <si>
+    <t>Standard Liege</t>
+  </si>
+  <si>
+    <t>Sutton Utd</t>
+  </si>
+  <si>
+    <t>Truro City</t>
+  </si>
+  <si>
+    <t>Solihull Moors</t>
+  </si>
+  <si>
+    <t>Oxford United</t>
+  </si>
+  <si>
+    <t>Mansfield Town</t>
+  </si>
+  <si>
+    <t>Aldershot Town</t>
   </si>
 </sst>
 </file>
@@ -1858,6 +1906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="List1"/>
   <dimension ref="A1:B397"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1918,6 +1967,9 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1952,11 +2004,17 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
+      <c r="B13" t="s">
+        <v>507</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
+      <c r="B14" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -2821,6 +2879,9 @@
       <c r="A125" t="s">
         <v>125</v>
       </c>
+      <c r="B125" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -2964,6 +3025,9 @@
       <c r="A144" t="s">
         <v>144</v>
       </c>
+      <c r="B144" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -3284,6 +3348,9 @@
       <c r="A187" t="s">
         <v>190</v>
       </c>
+      <c r="B187" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
@@ -3609,6 +3676,9 @@
       <c r="A231" t="s">
         <v>234</v>
       </c>
+      <c r="B231" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
@@ -3912,6 +3982,9 @@
       <c r="A270" t="s">
         <v>273</v>
       </c>
+      <c r="B270" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
@@ -4097,11 +4170,17 @@
       <c r="A295" t="s">
         <v>299</v>
       </c>
+      <c r="B295" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>300</v>
       </c>
+      <c r="B296" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
@@ -4346,6 +4425,9 @@
       <c r="A328" t="s">
         <v>332</v>
       </c>
+      <c r="B328" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
@@ -4464,7 +4546,7 @@
         <v>350</v>
       </c>
       <c r="B343" t="s">
-        <v>348</v>
+        <v>501</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
@@ -4492,6 +4574,9 @@
       <c r="A347" t="s">
         <v>354</v>
       </c>
+      <c r="B347" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
@@ -4545,6 +4630,9 @@
       <c r="A354" t="s">
         <v>361</v>
       </c>
+      <c r="B354" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
@@ -4635,6 +4723,9 @@
       <c r="A366" t="s">
         <v>373</v>
       </c>
+      <c r="B366" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
@@ -4852,6 +4943,9 @@
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>401</v>
+      </c>
+      <c r="B394" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
